--- a/Design/Excel/GameHot/Datas/Buqi/BuqiEventOption.xlsx
+++ b/Design/Excel/GameHot/Datas/Buqi/BuqiEventOption.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuqiEventOption" sheetId="1" r:id="R662cef73a321469d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BuqiEventOption" sheetId="1" r:id="R150acdf23eb849f1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -417,7 +417,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E4" t="str">
-        <x:v>照刻试锋</x:v>
+        <x:v>购买攻击装备</x:v>
       </x:c>
       <x:c r="F4" t="str">
         <x:v>Buqi.Content.EventOption.event_trial_stele_read.Name</x:v>
@@ -428,22 +428,22 @@
       <x:c r="H4" t="str">
         <x:v>fast</x:v>
       </x:c>
-      <x:c r="I4" t="str"/>
-      <x:c r="J4" t="str"/>
+      <x:c r="I4"/>
+      <x:c r="J4"/>
       <x:c r="K4" t="str">
         <x:v>Coins,1,None</x:v>
       </x:c>
       <x:c r="L4" t="str">
         <x:v>GrantItemTag,1,attack,0,event-trial-stele-attack</x:v>
       </x:c>
-      <x:c r="M4" t="str"/>
-      <x:c r="N4" t="str"/>
-      <x:c r="O4" t="str"/>
+      <x:c r="M4"/>
+      <x:c r="N4"/>
+      <x:c r="O4"/>
       <x:c r="P4" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q4" t="str">
-        <x:v>支付 1 灵石，从攻击子池获得一件普通小型器物。</x:v>
+        <x:v>支付 1 金币，从攻击子池获得一件普通小型装备。</x:v>
       </x:c>
       <x:c r="R4" t="str">
         <x:v>Buqi.Content.EventOption.event_trial_stele_read.Summary</x:v>
@@ -461,7 +461,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E5" t="str">
-        <x:v>以盾拓印</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="F5" t="str">
         <x:v>Buqi.Content.EventOption.event_trial_stele_brace.Name</x:v>
@@ -472,22 +472,22 @@
       <x:c r="H5" t="str">
         <x:v>shield</x:v>
       </x:c>
-      <x:c r="I5" t="str"/>
-      <x:c r="J5" t="str"/>
+      <x:c r="I5"/>
+      <x:c r="J5"/>
       <x:c r="K5" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L5" t="str">
         <x:v>TemporaryBuffer,6,None,1,event-trial-stele-buffer</x:v>
       </x:c>
-      <x:c r="M5" t="str"/>
-      <x:c r="N5" t="str"/>
-      <x:c r="O5" t="str"/>
+      <x:c r="M5"/>
+      <x:c r="N5"/>
+      <x:c r="O5"/>
       <x:c r="P5" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q5" t="str">
-        <x:v>下一战开场获得 6 点护体。</x:v>
+        <x:v>下一战开场获得 6 点护盾。</x:v>
       </x:c>
       <x:c r="R5" t="str">
         <x:v>Buqi.Content.EventOption.event_trial_stele_brace.Summary</x:v>
@@ -505,7 +505,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E6" t="str">
-        <x:v>记下碑序</x:v>
+        <x:v>获得 1 金币</x:v>
       </x:c>
       <x:c r="F6" t="str">
         <x:v>Buqi.Content.EventOption.event_trial_stele_leave.Name</x:v>
@@ -516,22 +516,22 @@
       <x:c r="H6" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I6" t="str"/>
-      <x:c r="J6" t="str"/>
+      <x:c r="I6"/>
+      <x:c r="J6"/>
       <x:c r="K6" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L6" t="str">
         <x:v>Coins,1,None,0,event-trial-stele-coin</x:v>
       </x:c>
-      <x:c r="M6" t="str"/>
-      <x:c r="N6" t="str"/>
-      <x:c r="O6" t="str"/>
+      <x:c r="M6"/>
+      <x:c r="N6"/>
+      <x:c r="O6"/>
       <x:c r="P6" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q6" t="str">
-        <x:v>获得 1 灵石。</x:v>
+        <x:v>获得 1 金币。</x:v>
       </x:c>
       <x:c r="R6" t="str">
         <x:v>Buqi.Content.EventOption.event_trial_stele_leave.Summary</x:v>
@@ -549,7 +549,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E7" t="str">
-        <x:v>买一剂</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="F7" t="str">
         <x:v>Buqi.Content.EventOption.event_herb_stall_dose.Name</x:v>
@@ -560,17 +560,17 @@
       <x:c r="H7" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I7" t="str"/>
-      <x:c r="J7" t="str"/>
+      <x:c r="I7"/>
+      <x:c r="J7"/>
       <x:c r="K7" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
       <x:c r="L7" t="str">
         <x:v>TemporaryHealing,8,None,1,event-herb-stall-heal</x:v>
       </x:c>
-      <x:c r="M7" t="str"/>
-      <x:c r="N7" t="str"/>
-      <x:c r="O7" t="str"/>
+      <x:c r="M7"/>
+      <x:c r="N7"/>
+      <x:c r="O7"/>
       <x:c r="P7" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -593,7 +593,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E8" t="str">
-        <x:v>换取药种</x:v>
+        <x:v>购买恢复装备</x:v>
       </x:c>
       <x:c r="F8" t="str">
         <x:v>Buqi.Content.EventOption.event_herb_stall_seed.Name</x:v>
@@ -604,22 +604,22 @@
       <x:c r="H8" t="str">
         <x:v>heal</x:v>
       </x:c>
-      <x:c r="I8" t="str"/>
-      <x:c r="J8" t="str"/>
+      <x:c r="I8"/>
+      <x:c r="J8"/>
       <x:c r="K8" t="str">
         <x:v>Coins,1,None</x:v>
       </x:c>
       <x:c r="L8" t="str">
         <x:v>GrantItemTag,1,regen,0,event-herb-stall-regen</x:v>
       </x:c>
-      <x:c r="M8" t="str"/>
-      <x:c r="N8" t="str"/>
-      <x:c r="O8" t="str"/>
+      <x:c r="M8"/>
+      <x:c r="N8"/>
+      <x:c r="O8"/>
       <x:c r="P8" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q8" t="str">
-        <x:v>支付 1 灵石，从恢复子池获得一件普通小型器物。</x:v>
+        <x:v>支付 1 金币，从恢复子池获得一件普通小型装备。</x:v>
       </x:c>
       <x:c r="R8" t="str">
         <x:v>Buqi.Content.EventOption.event_herb_stall_seed.Summary</x:v>
@@ -637,7 +637,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E9" t="str">
-        <x:v>帮忙理药</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
       <x:c r="F9" t="str">
         <x:v>Buqi.Content.EventOption.event_herb_stall_work.Name</x:v>
@@ -648,22 +648,22 @@
       <x:c r="H9" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I9" t="str"/>
-      <x:c r="J9" t="str"/>
+      <x:c r="I9"/>
+      <x:c r="J9"/>
       <x:c r="K9" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L9" t="str">
         <x:v>Coins,2,None,0,event-herb-stall-work</x:v>
       </x:c>
-      <x:c r="M9" t="str"/>
-      <x:c r="N9" t="str"/>
-      <x:c r="O9" t="str"/>
+      <x:c r="M9"/>
+      <x:c r="N9"/>
+      <x:c r="O9"/>
       <x:c r="P9" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q9" t="str">
-        <x:v>获得 2 灵石。</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="R9" t="str">
         <x:v>Buqi.Content.EventOption.event_herb_stall_work.Summary</x:v>
@@ -681,7 +681,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E10" t="str">
-        <x:v>补上甲片</x:v>
+        <x:v>强化护盾装备</x:v>
       </x:c>
       <x:c r="F10" t="str">
         <x:v>Buqi.Content.EventOption.event_broken_armor_fit.Name</x:v>
@@ -692,22 +692,22 @@
       <x:c r="H10" t="str">
         <x:v>shield</x:v>
       </x:c>
-      <x:c r="I10" t="str"/>
-      <x:c r="J10" t="str"/>
+      <x:c r="I10"/>
+      <x:c r="J10"/>
       <x:c r="K10" t="str">
         <x:v>Coins,1,None</x:v>
       </x:c>
       <x:c r="L10" t="str">
         <x:v>UpgradeItemTag,1,shield,0,event-broken-armor-upgrade</x:v>
       </x:c>
-      <x:c r="M10" t="str"/>
-      <x:c r="N10" t="str"/>
-      <x:c r="O10" t="str"/>
+      <x:c r="M10"/>
+      <x:c r="N10"/>
+      <x:c r="O10"/>
       <x:c r="P10" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q10" t="str">
-        <x:v>支付 1 灵石，将一件普通护体器物提升为改良。</x:v>
+        <x:v>支付 1 金币，将一件普通护盾装备提升为强化。</x:v>
       </x:c>
       <x:c r="R10" t="str">
         <x:v>Buqi.Content.EventOption.event_broken_armor_fit.Summary</x:v>
@@ -725,7 +725,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E11" t="str">
-        <x:v>拆取护片</x:v>
+        <x:v>过载换护盾装备</x:v>
       </x:c>
       <x:c r="F11" t="str">
         <x:v>Buqi.Content.EventOption.event_broken_armor_salvage.Name</x:v>
@@ -736,22 +736,22 @@
       <x:c r="H11" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I11" t="str"/>
-      <x:c r="J11" t="str"/>
+      <x:c r="I11"/>
+      <x:c r="J11"/>
       <x:c r="K11" t="str">
         <x:v>NoiseDebt,1,None</x:v>
       </x:c>
       <x:c r="L11" t="str">
         <x:v>GrantItemTag,1,shield,0,event-broken-armor-item</x:v>
       </x:c>
-      <x:c r="M11" t="str"/>
-      <x:c r="N11" t="str"/>
-      <x:c r="O11" t="str"/>
+      <x:c r="M11"/>
+      <x:c r="N11"/>
+      <x:c r="O11"/>
       <x:c r="P11" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q11" t="str">
-        <x:v>带 1 点失衡进入下一战，获得一件普通护体器物。</x:v>
+        <x:v>带 1 点过载进入下一战，获得一件普通护盾装备。</x:v>
       </x:c>
       <x:c r="R11" t="str">
         <x:v>Buqi.Content.EventOption.event_broken_armor_salvage.Summary</x:v>
@@ -769,7 +769,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E12" t="str">
-        <x:v>量下裂口</x:v>
+        <x:v>获得护盾购买折扣</x:v>
       </x:c>
       <x:c r="F12" t="str">
         <x:v>Buqi.Content.EventOption.event_broken_armor_measure.Name</x:v>
@@ -780,22 +780,22 @@
       <x:c r="H12" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I12" t="str"/>
-      <x:c r="J12" t="str"/>
+      <x:c r="I12"/>
+      <x:c r="J12"/>
       <x:c r="K12" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L12" t="str">
         <x:v>ShopDiscount,1,shield,1,event-broken-armor-discount</x:v>
       </x:c>
-      <x:c r="M12" t="str"/>
-      <x:c r="N12" t="str"/>
-      <x:c r="O12" t="str"/>
+      <x:c r="M12"/>
+      <x:c r="N12"/>
+      <x:c r="O12"/>
       <x:c r="P12" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q12" t="str">
-        <x:v>本日下一件护体器物少花 1 灵石。</x:v>
+        <x:v>本日下一件护盾装备少花 1 金币。</x:v>
       </x:c>
       <x:c r="R12" t="str">
         <x:v>Buqi.Content.EventOption.event_broken_armor_measure.Summary</x:v>
@@ -813,7 +813,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E13" t="str">
-        <x:v>买下杂包</x:v>
+        <x:v>获得桥接装备</x:v>
       </x:c>
       <x:c r="F13" t="str">
         <x:v>Buqi.Content.EventOption.event_cloud_peddler_bundle.Name</x:v>
@@ -824,22 +824,22 @@
       <x:c r="H13" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I13" t="str"/>
-      <x:c r="J13" t="str"/>
+      <x:c r="I13"/>
+      <x:c r="J13"/>
       <x:c r="K13" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
       <x:c r="L13" t="str">
         <x:v>GrantItemTag,1,bridge,0,event-cloud-peddler-bridge</x:v>
       </x:c>
-      <x:c r="M13" t="str"/>
-      <x:c r="N13" t="str"/>
-      <x:c r="O13" t="str"/>
+      <x:c r="M13"/>
+      <x:c r="N13"/>
+      <x:c r="O13"/>
       <x:c r="P13" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q13" t="str">
-        <x:v>获得一件普通桥接器物。</x:v>
+        <x:v>获得一件普通桥接装备。</x:v>
       </x:c>
       <x:c r="R13" t="str">
         <x:v>Buqi.Content.EventOption.event_cloud_peddler_bundle.Summary</x:v>
@@ -857,7 +857,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E14" t="str">
-        <x:v>买路线图</x:v>
+        <x:v>获得免费刷新</x:v>
       </x:c>
       <x:c r="F14" t="str">
         <x:v>Buqi.Content.EventOption.event_cloud_peddler_map.Name</x:v>
@@ -868,17 +868,17 @@
       <x:c r="H14" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I14" t="str"/>
-      <x:c r="J14" t="str"/>
+      <x:c r="I14"/>
+      <x:c r="J14"/>
       <x:c r="K14" t="str">
         <x:v>Coins,1,None</x:v>
       </x:c>
       <x:c r="L14" t="str">
         <x:v>FreeRefresh,1,None,1,event-cloud-peddler-refresh</x:v>
       </x:c>
-      <x:c r="M14" t="str"/>
-      <x:c r="N14" t="str"/>
-      <x:c r="O14" t="str"/>
+      <x:c r="M14"/>
+      <x:c r="N14"/>
+      <x:c r="O14"/>
       <x:c r="P14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -901,7 +901,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E15" t="str">
-        <x:v>替他叫卖</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
       <x:c r="F15" t="str">
         <x:v>Buqi.Content.EventOption.event_cloud_peddler_bargain.Name</x:v>
@@ -912,22 +912,22 @@
       <x:c r="H15" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I15" t="str"/>
-      <x:c r="J15" t="str"/>
+      <x:c r="I15"/>
+      <x:c r="J15"/>
       <x:c r="K15" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L15" t="str">
         <x:v>Coins,2,None,0,event-cloud-peddler-work</x:v>
       </x:c>
-      <x:c r="M15" t="str"/>
-      <x:c r="N15" t="str"/>
-      <x:c r="O15" t="str"/>
+      <x:c r="M15"/>
+      <x:c r="N15"/>
+      <x:c r="O15"/>
       <x:c r="P15" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q15" t="str">
-        <x:v>获得 2 灵石。</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="R15" t="str">
         <x:v>Buqi.Content.EventOption.event_cloud_peddler_bargain.Summary</x:v>
@@ -945,7 +945,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E16" t="str">
-        <x:v>当场淬火</x:v>
+        <x:v>强化普通装备</x:v>
       </x:c>
       <x:c r="F16" t="str">
         <x:v>Buqi.Content.EventOption.event_borrowed_flame_temper.Name</x:v>
@@ -956,22 +956,22 @@
       <x:c r="H16" t="str">
         <x:v>Normal</x:v>
       </x:c>
-      <x:c r="I16" t="str"/>
-      <x:c r="J16" t="str"/>
+      <x:c r="I16"/>
+      <x:c r="J16"/>
       <x:c r="K16" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
       <x:c r="L16" t="str">
         <x:v>UpgradeItemTag,1,any,0,event-borrowed-flame-upgrade</x:v>
       </x:c>
-      <x:c r="M16" t="str"/>
-      <x:c r="N16" t="str"/>
-      <x:c r="O16" t="str"/>
+      <x:c r="M16"/>
+      <x:c r="N16"/>
+      <x:c r="O16"/>
       <x:c r="P16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q16" t="str">
-        <x:v>支付 2 灵石，将一件普通器物提升为改良。</x:v>
+        <x:v>支付 2 金币，将一件普通装备提升为强化。</x:v>
       </x:c>
       <x:c r="R16" t="str">
         <x:v>Buqi.Content.EventOption.event_borrowed_flame_temper.Summary</x:v>
@@ -989,7 +989,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E17" t="str">
-        <x:v>借走火种</x:v>
+        <x:v>过载换升级折扣</x:v>
       </x:c>
       <x:c r="F17" t="str">
         <x:v>Buqi.Content.EventOption.event_borrowed_flame_carry.Name</x:v>
@@ -1000,8 +1000,8 @@
       <x:c r="H17" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I17" t="str"/>
-      <x:c r="J17" t="str"/>
+      <x:c r="I17"/>
+      <x:c r="J17"/>
       <x:c r="K17" t="str">
         <x:v>NoiseDebt,2,None</x:v>
       </x:c>
@@ -1011,7 +1011,7 @@
       <x:c r="M17" t="str">
         <x:v>borrowed_flame</x:v>
       </x:c>
-      <x:c r="N17" t="str"/>
+      <x:c r="N17"/>
       <x:c r="O17" t="str">
         <x:v>event-roving-furnace</x:v>
       </x:c>
@@ -1019,7 +1019,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q17" t="str">
-        <x:v>未来两日首次升级少花 2 灵石；下一战增加 2 点失衡。</x:v>
+        <x:v>未来两日首次升级少花 2 金币；下一战增加 2 点过载。</x:v>
       </x:c>
       <x:c r="R17" t="str">
         <x:v>Buqi.Content.EventOption.event_borrowed_flame_carry.Summary</x:v>
@@ -1037,7 +1037,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E18" t="str">
-        <x:v>转卖余炭</x:v>
+        <x:v>获得 2 金币</x:v>
       </x:c>
       <x:c r="F18" t="str">
         <x:v>Buqi.Content.EventOption.event_borrowed_flame_sell.Name</x:v>
@@ -1048,22 +1048,22 @@
       <x:c r="H18" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I18" t="str"/>
-      <x:c r="J18" t="str"/>
+      <x:c r="I18"/>
+      <x:c r="J18"/>
       <x:c r="K18" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L18" t="str">
         <x:v>Coins,2,None,0,event-borrowed-flame-sell</x:v>
       </x:c>
-      <x:c r="M18" t="str"/>
-      <x:c r="N18" t="str"/>
-      <x:c r="O18" t="str"/>
+      <x:c r="M18"/>
+      <x:c r="N18"/>
+      <x:c r="O18"/>
       <x:c r="P18" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q18" t="str">
-        <x:v>获得 2 灵石。</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="R18" t="str">
         <x:v>Buqi.Content.EventOption.event_borrowed_flame_sell.Summary</x:v>
@@ -1081,7 +1081,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E19" t="str">
-        <x:v>接回弦线</x:v>
+        <x:v>强化桥接装备</x:v>
       </x:c>
       <x:c r="F19" t="str">
         <x:v>Buqi.Content.EventOption.event_broken_mechanism_repair.Name</x:v>
@@ -1092,22 +1092,22 @@
       <x:c r="H19" t="str">
         <x:v>bridge</x:v>
       </x:c>
-      <x:c r="I19" t="str"/>
-      <x:c r="J19" t="str"/>
+      <x:c r="I19"/>
+      <x:c r="J19"/>
       <x:c r="K19" t="str">
         <x:v>Coins,1,None</x:v>
       </x:c>
       <x:c r="L19" t="str">
         <x:v>UpgradeItemTag,1,bridge,0,event-broken-mechanism-upgrade</x:v>
       </x:c>
-      <x:c r="M19" t="str"/>
-      <x:c r="N19" t="str"/>
-      <x:c r="O19" t="str"/>
+      <x:c r="M19"/>
+      <x:c r="N19"/>
+      <x:c r="O19"/>
       <x:c r="P19" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q19" t="str">
-        <x:v>支付 1 灵石，将一件普通桥接器物提升为改良。</x:v>
+        <x:v>支付 1 金币，将一件普通桥接装备提升为强化。</x:v>
       </x:c>
       <x:c r="R19" t="str">
         <x:v>Buqi.Content.EventOption.event_broken_mechanism_repair.Summary</x:v>
@@ -1125,7 +1125,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E20" t="str">
-        <x:v>拆走转轴</x:v>
+        <x:v>获得桥接装备</x:v>
       </x:c>
       <x:c r="F20" t="str">
         <x:v>Buqi.Content.EventOption.event_broken_mechanism_take.Name</x:v>
@@ -1136,22 +1136,22 @@
       <x:c r="H20" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I20" t="str"/>
-      <x:c r="J20" t="str"/>
+      <x:c r="I20"/>
+      <x:c r="J20"/>
       <x:c r="K20" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L20" t="str">
         <x:v>GrantItemTag,1,bridge,0,event-broken-mechanism-item</x:v>
       </x:c>
-      <x:c r="M20" t="str"/>
-      <x:c r="N20" t="str"/>
-      <x:c r="O20" t="str"/>
+      <x:c r="M20"/>
+      <x:c r="N20"/>
+      <x:c r="O20"/>
       <x:c r="P20" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q20" t="str">
-        <x:v>获得一件普通桥接器物。</x:v>
+        <x:v>获得一件普通桥接装备。</x:v>
       </x:c>
       <x:c r="R20" t="str">
         <x:v>Buqi.Content.EventOption.event_broken_mechanism_take.Summary</x:v>
@@ -1169,7 +1169,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E21" t="str">
-        <x:v>空转试机</x:v>
+        <x:v>过载换相邻加速</x:v>
       </x:c>
       <x:c r="F21" t="str">
         <x:v>Buqi.Content.EventOption.event_broken_mechanism_test.Name</x:v>
@@ -1180,22 +1180,22 @@
       <x:c r="H21" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I21" t="str"/>
-      <x:c r="J21" t="str"/>
+      <x:c r="I21"/>
+      <x:c r="J21"/>
       <x:c r="K21" t="str">
         <x:v>NoiseDebt,1,None</x:v>
       </x:c>
       <x:c r="L21" t="str">
         <x:v>TemporaryHaste,800,adjacent,1,event-broken-mechanism-haste</x:v>
       </x:c>
-      <x:c r="M21" t="str"/>
-      <x:c r="N21" t="str"/>
-      <x:c r="O21" t="str"/>
+      <x:c r="M21"/>
+      <x:c r="N21"/>
+      <x:c r="O21"/>
       <x:c r="P21" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q21" t="str">
-        <x:v>下一战增加 1 点失衡；相邻器物开场加速 800，持续 30 tick。</x:v>
+        <x:v>下一战增加 1 点过载；相邻装备开场加速 800，持续 30 时间单位。</x:v>
       </x:c>
       <x:c r="R21" t="str">
         <x:v>Buqi.Content.EventOption.event_broken_mechanism_test.Summary</x:v>
@@ -1213,7 +1213,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E22" t="str">
-        <x:v>记一笔赊账</x:v>
+        <x:v>延后结算换 4 金币</x:v>
       </x:c>
       <x:c r="F22" t="str">
         <x:v>Buqi.Content.EventOption.event_nameless_ledger_borrow.Name</x:v>
@@ -1224,8 +1224,8 @@
       <x:c r="H22" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I22" t="str"/>
-      <x:c r="J22" t="str"/>
+      <x:c r="I22"/>
+      <x:c r="J22"/>
       <x:c r="K22" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
@@ -1235,7 +1235,7 @@
       <x:c r="M22" t="str">
         <x:v>ledger_owed</x:v>
       </x:c>
-      <x:c r="N22" t="str"/>
+      <x:c r="N22"/>
       <x:c r="O22" t="str">
         <x:v>event-ledger-collector</x:v>
       </x:c>
@@ -1243,7 +1243,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q22" t="str">
-        <x:v>获得 4 灵石；两日后账主回访。</x:v>
+        <x:v>获得 4 金币；两日后触发欠款结算事件。</x:v>
       </x:c>
       <x:c r="R22" t="str">
         <x:v>Buqi.Content.EventOption.event_nameless_ledger_borrow.Summary</x:v>
@@ -1261,7 +1261,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E23" t="str">
-        <x:v>替它清账</x:v>
+        <x:v>获得两次免费刷新</x:v>
       </x:c>
       <x:c r="F23" t="str">
         <x:v>Buqi.Content.EventOption.event_nameless_ledger_audit.Name</x:v>
@@ -1272,8 +1272,8 @@
       <x:c r="H23" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I23" t="str"/>
-      <x:c r="J23" t="str"/>
+      <x:c r="I23"/>
+      <x:c r="J23"/>
       <x:c r="K23" t="str">
         <x:v>Coins,1,None</x:v>
       </x:c>
@@ -1283,8 +1283,8 @@
       <x:c r="M23" t="str">
         <x:v>ledger_closed</x:v>
       </x:c>
-      <x:c r="N23" t="str"/>
-      <x:c r="O23" t="str"/>
+      <x:c r="N23"/>
+      <x:c r="O23"/>
       <x:c r="P23" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1307,7 +1307,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E24" t="str">
-        <x:v>合上账册</x:v>
+        <x:v>获得 1 金币</x:v>
       </x:c>
       <x:c r="F24" t="str">
         <x:v>Buqi.Content.EventOption.event_nameless_ledger_leave.Name</x:v>
@@ -1318,8 +1318,8 @@
       <x:c r="H24" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I24" t="str"/>
-      <x:c r="J24" t="str"/>
+      <x:c r="I24"/>
+      <x:c r="J24"/>
       <x:c r="K24" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
@@ -1329,13 +1329,13 @@
       <x:c r="M24" t="str">
         <x:v>ledger_closed</x:v>
       </x:c>
-      <x:c r="N24" t="str"/>
-      <x:c r="O24" t="str"/>
+      <x:c r="N24"/>
+      <x:c r="O24"/>
       <x:c r="P24" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q24" t="str">
-        <x:v>获得 1 灵石。</x:v>
+        <x:v>获得 1 金币。</x:v>
       </x:c>
       <x:c r="R24" t="str">
         <x:v>Buqi.Content.EventOption.event_nameless_ledger_leave.Summary</x:v>
@@ -1353,7 +1353,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E25" t="str">
-        <x:v>借伞赶路</x:v>
+        <x:v>借用换开场护盾</x:v>
       </x:c>
       <x:c r="F25" t="str">
         <x:v>Buqi.Content.EventOption.event_rain_umbrella_borrow.Name</x:v>
@@ -1364,8 +1364,8 @@
       <x:c r="H25" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I25" t="str"/>
-      <x:c r="J25" t="str"/>
+      <x:c r="I25"/>
+      <x:c r="J25"/>
       <x:c r="K25" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
@@ -1375,7 +1375,7 @@
       <x:c r="M25" t="str">
         <x:v>umbrella_borrowed</x:v>
       </x:c>
-      <x:c r="N25" t="str"/>
+      <x:c r="N25"/>
       <x:c r="O25" t="str">
         <x:v>event-umbrella-return</x:v>
       </x:c>
@@ -1383,7 +1383,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="Q25" t="str">
-        <x:v>下一战开场获得 8 点护体；两日后归伞人回访。</x:v>
+        <x:v>下一战开场获得 8 点护盾；两日后触发借用结算事件。</x:v>
       </x:c>
       <x:c r="R25" t="str">
         <x:v>Buqi.Content.EventOption.event_rain_umbrella_borrow.Summary</x:v>
@@ -1401,7 +1401,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E26" t="str">
-        <x:v>买下旧伞</x:v>
+        <x:v>获得护盾装备</x:v>
       </x:c>
       <x:c r="F26" t="str">
         <x:v>Buqi.Content.EventOption.event_rain_umbrella_buy.Name</x:v>
@@ -1412,8 +1412,8 @@
       <x:c r="H26" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I26" t="str"/>
-      <x:c r="J26" t="str"/>
+      <x:c r="I26"/>
+      <x:c r="J26"/>
       <x:c r="K26" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
@@ -1423,13 +1423,13 @@
       <x:c r="M26" t="str">
         <x:v>umbrella_returned</x:v>
       </x:c>
-      <x:c r="N26" t="str"/>
-      <x:c r="O26" t="str"/>
+      <x:c r="N26"/>
+      <x:c r="O26"/>
       <x:c r="P26" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q26" t="str">
-        <x:v>获得一件普通护体器物。</x:v>
+        <x:v>获得一件普通护盾装备。</x:v>
       </x:c>
       <x:c r="R26" t="str">
         <x:v>Buqi.Content.EventOption.event_rain_umbrella_buy.Summary</x:v>
@@ -1447,7 +1447,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E27" t="str">
-        <x:v>檐下等雨</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="F27" t="str">
         <x:v>Buqi.Content.EventOption.event_rain_umbrella_wait.Name</x:v>
@@ -1458,17 +1458,17 @@
       <x:c r="H27" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I27" t="str"/>
-      <x:c r="J27" t="str"/>
+      <x:c r="I27"/>
+      <x:c r="J27"/>
       <x:c r="K27" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L27" t="str">
         <x:v>TemporaryHealing,5,None,1,event-rain-umbrella-rest</x:v>
       </x:c>
-      <x:c r="M27" t="str"/>
-      <x:c r="N27" t="str"/>
-      <x:c r="O27" t="str"/>
+      <x:c r="M27"/>
+      <x:c r="N27"/>
+      <x:c r="O27"/>
       <x:c r="P27" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1491,7 +1491,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E28" t="str">
-        <x:v>循痕运刃</x:v>
+        <x:v>升级攻击装备</x:v>
       </x:c>
       <x:c r="F28" t="str">
         <x:v>Buqi.Content.EventOption.event_sword_echo_follow.Name</x:v>
@@ -1502,22 +1502,22 @@
       <x:c r="H28" t="str">
         <x:v>fast</x:v>
       </x:c>
-      <x:c r="I28" t="str"/>
-      <x:c r="J28" t="str"/>
+      <x:c r="I28"/>
+      <x:c r="J28"/>
       <x:c r="K28" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
       <x:c r="L28" t="str">
         <x:v>UpgradeItemTag,1,attack,0,event-sword-echo-upgrade</x:v>
       </x:c>
-      <x:c r="M28" t="str"/>
-      <x:c r="N28" t="str"/>
-      <x:c r="O28" t="str"/>
+      <x:c r="M28"/>
+      <x:c r="N28"/>
+      <x:c r="O28"/>
       <x:c r="P28" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q28" t="str">
-        <x:v>支付 2 灵石，升级一件普通攻击器物。</x:v>
+        <x:v>支付 2 金币，升级一件普通攻击装备。</x:v>
       </x:c>
       <x:c r="R28" t="str">
         <x:v>Buqi.Content.EventOption.event_sword_echo_follow.Summary</x:v>
@@ -1535,7 +1535,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E29" t="str">
-        <x:v>以甲受痕</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="F29" t="str">
         <x:v>Buqi.Content.EventOption.event_sword_echo_deflect.Name</x:v>
@@ -1546,22 +1546,22 @@
       <x:c r="H29" t="str">
         <x:v>shield</x:v>
       </x:c>
-      <x:c r="I29" t="str"/>
-      <x:c r="J29" t="str"/>
+      <x:c r="I29"/>
+      <x:c r="J29"/>
       <x:c r="K29" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L29" t="str">
         <x:v>TemporaryBuffer,10,None,1,event-sword-echo-buffer</x:v>
       </x:c>
-      <x:c r="M29" t="str"/>
-      <x:c r="N29" t="str"/>
-      <x:c r="O29" t="str"/>
+      <x:c r="M29"/>
+      <x:c r="N29"/>
+      <x:c r="O29"/>
       <x:c r="P29" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q29" t="str">
-        <x:v>下一战开场获得 10 点护体。</x:v>
+        <x:v>下一战开场获得 10 点护盾。</x:v>
       </x:c>
       <x:c r="R29" t="str">
         <x:v>Buqi.Content.EventOption.event_sword_echo_deflect.Summary</x:v>
@@ -1579,7 +1579,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E30" t="str">
-        <x:v>拓下剑路</x:v>
+        <x:v>过载换加急改造</x:v>
       </x:c>
       <x:c r="F30" t="str">
         <x:v>Buqi.Content.EventOption.event_sword_echo_copy.Name</x:v>
@@ -1590,22 +1590,22 @@
       <x:c r="H30" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I30" t="str"/>
-      <x:c r="J30" t="str"/>
+      <x:c r="I30"/>
+      <x:c r="J30"/>
       <x:c r="K30" t="str">
         <x:v>NoiseDebt,2,None</x:v>
       </x:c>
       <x:c r="L30" t="str">
         <x:v>GrantRefinement,1,A-01,0,event-sword-echo-refine</x:v>
       </x:c>
-      <x:c r="M30" t="str"/>
-      <x:c r="N30" t="str"/>
-      <x:c r="O30" t="str"/>
+      <x:c r="M30"/>
+      <x:c r="N30"/>
+      <x:c r="O30"/>
       <x:c r="P30" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q30" t="str">
-        <x:v>下一战增加 2 点失衡，获得加急精炼。</x:v>
+        <x:v>下一战增加 2 点过载，获得加急改造。</x:v>
       </x:c>
       <x:c r="R30" t="str">
         <x:v>Buqi.Content.EventOption.event_sword_echo_copy.Summary</x:v>
@@ -1623,7 +1623,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E31" t="str">
-        <x:v>封住裂隙</x:v>
+        <x:v>升级护盾装备</x:v>
       </x:c>
       <x:c r="F31" t="str">
         <x:v>Buqi.Content.EventOption.event_wall_fissure_seal.Name</x:v>
@@ -1634,22 +1634,22 @@
       <x:c r="H31" t="str">
         <x:v>shield</x:v>
       </x:c>
-      <x:c r="I31" t="str"/>
-      <x:c r="J31" t="str"/>
+      <x:c r="I31"/>
+      <x:c r="J31"/>
       <x:c r="K31" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
       <x:c r="L31" t="str">
         <x:v>UpgradeItemTag,1,shield,0,event-wall-fissure-upgrade</x:v>
       </x:c>
-      <x:c r="M31" t="str"/>
-      <x:c r="N31" t="str"/>
-      <x:c r="O31" t="str"/>
+      <x:c r="M31"/>
+      <x:c r="N31"/>
+      <x:c r="O31"/>
       <x:c r="P31" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q31" t="str">
-        <x:v>支付 2 灵石，升级一件普通护体器物。</x:v>
+        <x:v>支付 2 金币，升级一件普通护盾装备。</x:v>
       </x:c>
       <x:c r="R31" t="str">
         <x:v>Buqi.Content.EventOption.event_wall_fissure_seal.Summary</x:v>
@@ -1667,7 +1667,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E32" t="str">
-        <x:v>立临时支架</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="F32" t="str">
         <x:v>Buqi.Content.EventOption.event_wall_fissure_brace.Name</x:v>
@@ -1678,22 +1678,22 @@
       <x:c r="H32" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I32" t="str"/>
-      <x:c r="J32" t="str"/>
+      <x:c r="I32"/>
+      <x:c r="J32"/>
       <x:c r="K32" t="str">
         <x:v>Coins,1,None</x:v>
       </x:c>
       <x:c r="L32" t="str">
         <x:v>TemporaryBuffer,12,None,1,event-wall-fissure-brace</x:v>
       </x:c>
-      <x:c r="M32" t="str"/>
-      <x:c r="N32" t="str"/>
-      <x:c r="O32" t="str"/>
+      <x:c r="M32"/>
+      <x:c r="N32"/>
+      <x:c r="O32"/>
       <x:c r="P32" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q32" t="str">
-        <x:v>下一战开场获得 12 点护体。</x:v>
+        <x:v>下一战开场获得 12 点护盾。</x:v>
       </x:c>
       <x:c r="R32" t="str">
         <x:v>Buqi.Content.EventOption.event_wall_fissure_brace.Summary</x:v>
@@ -1711,7 +1711,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E33" t="str">
-        <x:v>收走碎砖</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
       <x:c r="F33" t="str">
         <x:v>Buqi.Content.EventOption.event_wall_fissure_salvage.Name</x:v>
@@ -1722,22 +1722,22 @@
       <x:c r="H33" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I33" t="str"/>
-      <x:c r="J33" t="str"/>
+      <x:c r="I33"/>
+      <x:c r="J33"/>
       <x:c r="K33" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L33" t="str">
         <x:v>Coins,3,None,0,event-wall-fissure-coins</x:v>
       </x:c>
-      <x:c r="M33" t="str"/>
-      <x:c r="N33" t="str"/>
-      <x:c r="O33" t="str"/>
+      <x:c r="M33"/>
+      <x:c r="N33"/>
+      <x:c r="O33"/>
       <x:c r="P33" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q33" t="str">
-        <x:v>获得 3 灵石。</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
       <x:c r="R33" t="str">
         <x:v>Buqi.Content.EventOption.event_wall_fissure_salvage.Summary</x:v>
@@ -1755,7 +1755,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E34" t="str">
-        <x:v>引水入田</x:v>
+        <x:v>升级恢复装备</x:v>
       </x:c>
       <x:c r="F34" t="str">
         <x:v>Buqi.Content.EventOption.event_herb_water_divert.Name</x:v>
@@ -1766,22 +1766,22 @@
       <x:c r="H34" t="str">
         <x:v>heal</x:v>
       </x:c>
-      <x:c r="I34" t="str"/>
-      <x:c r="J34" t="str"/>
+      <x:c r="I34"/>
+      <x:c r="J34"/>
       <x:c r="K34" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
       <x:c r="L34" t="str">
         <x:v>UpgradeItemTag,1,heal,0,event-herb-water-upgrade</x:v>
       </x:c>
-      <x:c r="M34" t="str"/>
-      <x:c r="N34" t="str"/>
-      <x:c r="O34" t="str"/>
+      <x:c r="M34"/>
+      <x:c r="N34"/>
+      <x:c r="O34"/>
       <x:c r="P34" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q34" t="str">
-        <x:v>支付 2 灵石，升级一件普通恢复器物。</x:v>
+        <x:v>支付 2 金币，升级一件普通恢复装备。</x:v>
       </x:c>
       <x:c r="R34" t="str">
         <x:v>Buqi.Content.EventOption.event_herb_water_divert.Summary</x:v>
@@ -1799,7 +1799,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E35" t="str">
-        <x:v>平分水渠</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="F35" t="str">
         <x:v>Buqi.Content.EventOption.event_herb_water_share.Name</x:v>
@@ -1810,17 +1810,17 @@
       <x:c r="H35" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I35" t="str"/>
-      <x:c r="J35" t="str"/>
+      <x:c r="I35"/>
+      <x:c r="J35"/>
       <x:c r="K35" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L35" t="str">
         <x:v>TemporaryHealing,10,None,1,event-herb-water-heal</x:v>
       </x:c>
-      <x:c r="M35" t="str"/>
-      <x:c r="N35" t="str"/>
-      <x:c r="O35" t="str"/>
+      <x:c r="M35"/>
+      <x:c r="N35"/>
+      <x:c r="O35"/>
       <x:c r="P35" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1843,7 +1843,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E36" t="str">
-        <x:v>卖出水权</x:v>
+        <x:v>生命换 5 金币</x:v>
       </x:c>
       <x:c r="F36" t="str">
         <x:v>Buqi.Content.EventOption.event_herb_water_sell.Name</x:v>
@@ -1854,22 +1854,22 @@
       <x:c r="H36" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I36" t="str"/>
-      <x:c r="J36" t="str"/>
+      <x:c r="I36"/>
+      <x:c r="J36"/>
       <x:c r="K36" t="str">
         <x:v>Life,1,None</x:v>
       </x:c>
       <x:c r="L36" t="str">
         <x:v>Coins,5,None,0,event-herb-water-coins</x:v>
       </x:c>
-      <x:c r="M36" t="str"/>
-      <x:c r="N36" t="str"/>
-      <x:c r="O36" t="str"/>
+      <x:c r="M36"/>
+      <x:c r="N36"/>
+      <x:c r="O36"/>
       <x:c r="P36" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q36" t="str">
-        <x:v>失去 1 命，获得 5 灵石。</x:v>
+        <x:v>失去 1 命，获得 5 金币。</x:v>
       </x:c>
       <x:c r="R36" t="str">
         <x:v>Buqi.Content.EventOption.event_herb_water_sell.Summary</x:v>
@@ -1887,7 +1887,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E37" t="str">
-        <x:v>归还火种</x:v>
+        <x:v>结清欠款并获得改造</x:v>
       </x:c>
       <x:c r="F37" t="str">
         <x:v>Buqi.Content.EventOption.event_roving_furnace_return.Name</x:v>
@@ -1901,23 +1901,23 @@
       <x:c r="I37" t="str">
         <x:v>borrowed_flame</x:v>
       </x:c>
-      <x:c r="J37" t="str"/>
+      <x:c r="J37"/>
       <x:c r="K37" t="str">
         <x:v>Coins,1,None</x:v>
       </x:c>
       <x:c r="L37" t="str">
         <x:v>GrantRefinement,1,A-05,0,event-roving-furnace-return</x:v>
       </x:c>
-      <x:c r="M37" t="str"/>
+      <x:c r="M37"/>
       <x:c r="N37" t="str">
         <x:v>borrowed_flame</x:v>
       </x:c>
-      <x:c r="O37" t="str"/>
+      <x:c r="O37"/>
       <x:c r="P37" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q37" t="str">
-        <x:v>支付 1 灵石归还火种，获得稳流精炼。</x:v>
+        <x:v>支付 1 金币并结清欠款，获得稳定改造。</x:v>
       </x:c>
       <x:c r="R37" t="str">
         <x:v>Buqi.Content.EventOption.event_roving_furnace_return.Summary</x:v>
@@ -1935,7 +1935,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E38" t="str">
-        <x:v>留下火种</x:v>
+        <x:v>过载并升级灼烧装备</x:v>
       </x:c>
       <x:c r="F38" t="str">
         <x:v>Buqi.Content.EventOption.event_roving_furnace_keep.Name</x:v>
@@ -1949,23 +1949,23 @@
       <x:c r="I38" t="str">
         <x:v>borrowed_flame</x:v>
       </x:c>
-      <x:c r="J38" t="str"/>
+      <x:c r="J38"/>
       <x:c r="K38" t="str">
         <x:v>NoiseDebt,3,None</x:v>
       </x:c>
       <x:c r="L38" t="str">
         <x:v>UpgradeItemTag,1,burn,0,event-roving-furnace-keep</x:v>
       </x:c>
-      <x:c r="M38" t="str"/>
+      <x:c r="M38"/>
       <x:c r="N38" t="str">
         <x:v>borrowed_flame</x:v>
       </x:c>
-      <x:c r="O38" t="str"/>
+      <x:c r="O38"/>
       <x:c r="P38" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q38" t="str">
-        <x:v>下一战增加 3 点失衡，升级一件灼烧器物。</x:v>
+        <x:v>下一战增加 3 点过载，升级一件灼烧装备。</x:v>
       </x:c>
       <x:c r="R38" t="str">
         <x:v>Buqi.Content.EventOption.event_roving_furnace_keep.Summary</x:v>
@@ -1983,7 +1983,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E39" t="str">
-        <x:v>换成灵石</x:v>
+        <x:v>结清欠款并获得金币</x:v>
       </x:c>
       <x:c r="F39" t="str">
         <x:v>Buqi.Content.EventOption.event_roving_furnace_trade.Name</x:v>
@@ -1997,23 +1997,23 @@
       <x:c r="I39" t="str">
         <x:v>borrowed_flame</x:v>
       </x:c>
-      <x:c r="J39" t="str"/>
+      <x:c r="J39"/>
       <x:c r="K39" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L39" t="str">
         <x:v>Coins,3,None,0,event-roving-furnace-trade</x:v>
       </x:c>
-      <x:c r="M39" t="str"/>
+      <x:c r="M39"/>
       <x:c r="N39" t="str">
         <x:v>borrowed_flame</x:v>
       </x:c>
-      <x:c r="O39" t="str"/>
+      <x:c r="O39"/>
       <x:c r="P39" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q39" t="str">
-        <x:v>获得 3 灵石并结清火种。</x:v>
+        <x:v>获得 3 金币并结清欠款。</x:v>
       </x:c>
       <x:c r="R39" t="str">
         <x:v>Buqi.Content.EventOption.event_roving_furnace_trade.Summary</x:v>
@@ -2031,7 +2031,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E40" t="str">
-        <x:v>照数归还</x:v>
+        <x:v>支付欠款换免费刷新</x:v>
       </x:c>
       <x:c r="F40" t="str">
         <x:v>Buqi.Content.EventOption.event_ledger_collector_pay.Name</x:v>
@@ -2045,7 +2045,7 @@
       <x:c r="I40" t="str">
         <x:v>ledger_owed</x:v>
       </x:c>
-      <x:c r="J40" t="str"/>
+      <x:c r="J40"/>
       <x:c r="K40" t="str">
         <x:v>Coins,3,None</x:v>
       </x:c>
@@ -2058,12 +2058,12 @@
       <x:c r="N40" t="str">
         <x:v>ledger_owed</x:v>
       </x:c>
-      <x:c r="O40" t="str"/>
+      <x:c r="O40"/>
       <x:c r="P40" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q40" t="str">
-        <x:v>支付 3 灵石，本日获得 1 次免费刷新。</x:v>
+        <x:v>支付 3 金币，本日获得 1 次免费刷新。</x:v>
       </x:c>
       <x:c r="R40" t="str">
         <x:v>Buqi.Content.EventOption.event_ledger_collector_pay.Summary</x:v>
@@ -2081,7 +2081,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E41" t="str">
-        <x:v>替他收账</x:v>
+        <x:v>结清欠款并获得金币</x:v>
       </x:c>
       <x:c r="F41" t="str">
         <x:v>Buqi.Content.EventOption.event_ledger_collector_work.Name</x:v>
@@ -2095,7 +2095,7 @@
       <x:c r="I41" t="str">
         <x:v>ledger_owed</x:v>
       </x:c>
-      <x:c r="J41" t="str"/>
+      <x:c r="J41"/>
       <x:c r="K41" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
@@ -2108,12 +2108,12 @@
       <x:c r="N41" t="str">
         <x:v>ledger_owed</x:v>
       </x:c>
-      <x:c r="O41" t="str"/>
+      <x:c r="O41"/>
       <x:c r="P41" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q41" t="str">
-        <x:v>获得 1 灵石并结清账目。</x:v>
+        <x:v>获得 1 金币并结清账目。</x:v>
       </x:c>
       <x:c r="R41" t="str">
         <x:v>Buqi.Content.EventOption.event_ledger_collector_work.Summary</x:v>
@@ -2131,7 +2131,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E42" t="str">
-        <x:v>拒绝认账</x:v>
+        <x:v>拒付并承受惩罚</x:v>
       </x:c>
       <x:c r="F42" t="str">
         <x:v>Buqi.Content.EventOption.event_ledger_collector_default.Name</x:v>
@@ -2145,7 +2145,7 @@
       <x:c r="I42" t="str">
         <x:v>ledger_owed</x:v>
       </x:c>
-      <x:c r="J42" t="str"/>
+      <x:c r="J42"/>
       <x:c r="K42" t="str">
         <x:v>Life,1,None</x:v>
       </x:c>
@@ -2158,12 +2158,12 @@
       <x:c r="N42" t="str">
         <x:v>ledger_owed</x:v>
       </x:c>
-      <x:c r="O42" t="str"/>
+      <x:c r="O42"/>
       <x:c r="P42" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q42" t="str">
-        <x:v>失去 1 命；下一战增加 2 点失衡。</x:v>
+        <x:v>失去 1 命；下一战增加 2 点过载。</x:v>
       </x:c>
       <x:c r="R42" t="str">
         <x:v>Buqi.Content.EventOption.event_ledger_collector_default.Summary</x:v>
@@ -2181,7 +2181,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E43" t="str">
-        <x:v>原样归还</x:v>
+        <x:v>归还并获得金币</x:v>
       </x:c>
       <x:c r="F43" t="str">
         <x:v>Buqi.Content.EventOption.event_umbrella_return_return.Name</x:v>
@@ -2195,7 +2195,7 @@
       <x:c r="I43" t="str">
         <x:v>umbrella_borrowed</x:v>
       </x:c>
-      <x:c r="J43" t="str"/>
+      <x:c r="J43"/>
       <x:c r="K43" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
@@ -2208,12 +2208,12 @@
       <x:c r="N43" t="str">
         <x:v>umbrella_borrowed</x:v>
       </x:c>
-      <x:c r="O43" t="str"/>
+      <x:c r="O43"/>
       <x:c r="P43" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q43" t="str">
-        <x:v>获得 2 灵石。</x:v>
+        <x:v>获得 2 金币。</x:v>
       </x:c>
       <x:c r="R43" t="str">
         <x:v>Buqi.Content.EventOption.event_umbrella_return_return.Summary</x:v>
@@ -2231,7 +2231,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E44" t="str">
-        <x:v>修好再还</x:v>
+        <x:v>支付金币换改造</x:v>
       </x:c>
       <x:c r="F44" t="str">
         <x:v>Buqi.Content.EventOption.event_umbrella_return_repair.Name</x:v>
@@ -2245,7 +2245,7 @@
       <x:c r="I44" t="str">
         <x:v>umbrella_borrowed</x:v>
       </x:c>
-      <x:c r="J44" t="str"/>
+      <x:c r="J44"/>
       <x:c r="K44" t="str">
         <x:v>Coins,1,None</x:v>
       </x:c>
@@ -2258,12 +2258,12 @@
       <x:c r="N44" t="str">
         <x:v>umbrella_borrowed</x:v>
       </x:c>
-      <x:c r="O44" t="str"/>
+      <x:c r="O44"/>
       <x:c r="P44" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q44" t="str">
-        <x:v>支付 1 灵石，获得可靠精炼。</x:v>
+        <x:v>支付 1 金币，获得可靠改造。</x:v>
       </x:c>
       <x:c r="R44" t="str">
         <x:v>Buqi.Content.EventOption.event_umbrella_return_repair.Summary</x:v>
@@ -2281,7 +2281,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E45" t="str">
-        <x:v>留下旧伞</x:v>
+        <x:v>生命换强化护盾装备</x:v>
       </x:c>
       <x:c r="F45" t="str">
         <x:v>Buqi.Content.EventOption.event_umbrella_return_keep.Name</x:v>
@@ -2295,7 +2295,7 @@
       <x:c r="I45" t="str">
         <x:v>umbrella_borrowed</x:v>
       </x:c>
-      <x:c r="J45" t="str"/>
+      <x:c r="J45"/>
       <x:c r="K45" t="str">
         <x:v>Life,1,None</x:v>
       </x:c>
@@ -2308,12 +2308,12 @@
       <x:c r="N45" t="str">
         <x:v>umbrella_borrowed</x:v>
       </x:c>
-      <x:c r="O45" t="str"/>
+      <x:c r="O45"/>
       <x:c r="P45" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q45" t="str">
-        <x:v>失去 1 命，获得一件改良护体器物。</x:v>
+        <x:v>失去 1 命，获得一件强化护盾装备。</x:v>
       </x:c>
       <x:c r="R45" t="str">
         <x:v>Buqi.Content.EventOption.event_umbrella_return_keep.Summary</x:v>
@@ -2331,7 +2331,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E46" t="str">
-        <x:v>正面入阵</x:v>
+        <x:v>过载并升级反制装备</x:v>
       </x:c>
       <x:c r="F46" t="str">
         <x:v>Buqi.Content.EventOption.event_headwind_array_enter.Name</x:v>
@@ -2342,22 +2342,22 @@
       <x:c r="H46" t="str">
         <x:v>counter</x:v>
       </x:c>
-      <x:c r="I46" t="str"/>
-      <x:c r="J46" t="str"/>
+      <x:c r="I46"/>
+      <x:c r="J46"/>
       <x:c r="K46" t="str">
         <x:v>NoiseDebt,2,None</x:v>
       </x:c>
       <x:c r="L46" t="str">
         <x:v>UpgradeItemTag,1,counter,0,event-headwind-array-upgrade</x:v>
       </x:c>
-      <x:c r="M46" t="str"/>
-      <x:c r="N46" t="str"/>
-      <x:c r="O46" t="str"/>
+      <x:c r="M46"/>
+      <x:c r="N46"/>
+      <x:c r="O46"/>
       <x:c r="P46" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q46" t="str">
-        <x:v>下一战增加 2 点失衡，升级一件反制器物。</x:v>
+        <x:v>下一战增加 2 点过载，升级一件反制装备。</x:v>
       </x:c>
       <x:c r="R46" t="str">
         <x:v>Buqi.Content.EventOption.event_headwind_array_enter.Summary</x:v>
@@ -2375,7 +2375,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E47" t="str">
-        <x:v>以镇心铃定阵</x:v>
+        <x:v>支付金币换相邻加速</x:v>
       </x:c>
       <x:c r="F47" t="str">
         <x:v>Buqi.Content.EventOption.event_headwind_array_anchor.Name</x:v>
@@ -2386,22 +2386,22 @@
       <x:c r="H47" t="str">
         <x:v>shared</x:v>
       </x:c>
-      <x:c r="I47" t="str"/>
-      <x:c r="J47" t="str"/>
+      <x:c r="I47"/>
+      <x:c r="J47"/>
       <x:c r="K47" t="str">
         <x:v>Coins,1,None</x:v>
       </x:c>
       <x:c r="L47" t="str">
         <x:v>TemporaryHaste,1000,adjacent,1,event-headwind-array-haste</x:v>
       </x:c>
-      <x:c r="M47" t="str"/>
-      <x:c r="N47" t="str"/>
-      <x:c r="O47" t="str"/>
+      <x:c r="M47"/>
+      <x:c r="N47"/>
+      <x:c r="O47"/>
       <x:c r="P47" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q47" t="str">
-        <x:v>支付 1 灵石；下一战相邻器物开场加速 1000。</x:v>
+        <x:v>支付 1 金币；下一战相邻装备开场加速 1000。</x:v>
       </x:c>
       <x:c r="R47" t="str">
         <x:v>Buqi.Content.EventOption.event_headwind_array_anchor.Summary</x:v>
@@ -2419,7 +2419,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E48" t="str">
-        <x:v>阵外观风</x:v>
+        <x:v>获得反制购买折扣</x:v>
       </x:c>
       <x:c r="F48" t="str">
         <x:v>Buqi.Content.EventOption.event_headwind_array_observe.Name</x:v>
@@ -2430,22 +2430,22 @@
       <x:c r="H48" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I48" t="str"/>
-      <x:c r="J48" t="str"/>
+      <x:c r="I48"/>
+      <x:c r="J48"/>
       <x:c r="K48" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L48" t="str">
         <x:v>ShopDiscount,1,counter,1,event-headwind-array-discount</x:v>
       </x:c>
-      <x:c r="M48" t="str"/>
-      <x:c r="N48" t="str"/>
-      <x:c r="O48" t="str"/>
+      <x:c r="M48"/>
+      <x:c r="N48"/>
+      <x:c r="O48"/>
       <x:c r="P48" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q48" t="str">
-        <x:v>本日下一件反制器物少花 1 灵石。</x:v>
+        <x:v>本日下一件反制装备少花 1 金币。</x:v>
       </x:c>
       <x:c r="R48" t="str">
         <x:v>Buqi.Content.EventOption.event_headwind_array_observe.Summary</x:v>
@@ -2463,7 +2463,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E49" t="str">
-        <x:v>卖出闲器</x:v>
+        <x:v>卖出起手装备</x:v>
       </x:c>
       <x:c r="F49" t="str">
         <x:v>Buqi.Content.EventOption.event_three_bidders_sell.Name</x:v>
@@ -2474,22 +2474,22 @@
       <x:c r="H49" t="str">
         <x:v>starter</x:v>
       </x:c>
-      <x:c r="I49" t="str"/>
-      <x:c r="J49" t="str"/>
+      <x:c r="I49"/>
+      <x:c r="J49"/>
       <x:c r="K49" t="str">
         <x:v>ItemTag,1,starter</x:v>
       </x:c>
       <x:c r="L49" t="str">
         <x:v>Coins,5,None,0,event-three-bidders-sell</x:v>
       </x:c>
-      <x:c r="M49" t="str"/>
-      <x:c r="N49" t="str"/>
-      <x:c r="O49" t="str"/>
+      <x:c r="M49"/>
+      <x:c r="N49"/>
+      <x:c r="O49"/>
       <x:c r="P49" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q49" t="str">
-        <x:v>移除一件起手器物，获得 5 灵石。</x:v>
+        <x:v>移除一件起手装备，获得 5 金币。</x:v>
       </x:c>
       <x:c r="R49" t="str">
         <x:v>Buqi.Content.EventOption.event_three_bidders_sell.Summary</x:v>
@@ -2507,7 +2507,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E50" t="str">
-        <x:v>压价竞买</x:v>
+        <x:v>获得强化核心装备</x:v>
       </x:c>
       <x:c r="F50" t="str">
         <x:v>Buqi.Content.EventOption.event_three_bidders_bid.Name</x:v>
@@ -2518,22 +2518,22 @@
       <x:c r="H50" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I50" t="str"/>
-      <x:c r="J50" t="str"/>
+      <x:c r="I50"/>
+      <x:c r="J50"/>
       <x:c r="K50" t="str">
         <x:v>Coins,3,None</x:v>
       </x:c>
       <x:c r="L50" t="str">
         <x:v>GrantItemTag,1,core,0,event-three-bidders-core</x:v>
       </x:c>
-      <x:c r="M50" t="str"/>
-      <x:c r="N50" t="str"/>
-      <x:c r="O50" t="str"/>
+      <x:c r="M50"/>
+      <x:c r="N50"/>
+      <x:c r="O50"/>
       <x:c r="P50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q50" t="str">
-        <x:v>获得一件改良核心器物。</x:v>
+        <x:v>获得一件强化核心装备。</x:v>
       </x:c>
       <x:c r="R50" t="str">
         <x:v>Buqi.Content.EventOption.event_three_bidders_bid.Summary</x:v>
@@ -2551,7 +2551,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E51" t="str">
-        <x:v>押到第九日</x:v>
+        <x:v>投资至第九日</x:v>
       </x:c>
       <x:c r="F51" t="str">
         <x:v>Buqi.Content.EventOption.event_three_bidders_stake.Name</x:v>
@@ -2562,8 +2562,8 @@
       <x:c r="H51" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I51" t="str"/>
-      <x:c r="J51" t="str"/>
+      <x:c r="I51"/>
+      <x:c r="J51"/>
       <x:c r="K51" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
@@ -2573,7 +2573,7 @@
       <x:c r="M51" t="str">
         <x:v>auction_claim</x:v>
       </x:c>
-      <x:c r="N51" t="str"/>
+      <x:c r="N51"/>
       <x:c r="O51" t="str">
         <x:v>event-day-nine-ledger</x:v>
       </x:c>
@@ -2581,7 +2581,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Q51" t="str">
-        <x:v>支付 2 灵石，第九日按当前构筑回收。</x:v>
+        <x:v>支付 2 金币，第九日按当前构筑回收。</x:v>
       </x:c>
       <x:c r="R51" t="str">
         <x:v>Buqi.Content.EventOption.event_three_bidders_stake.Summary</x:v>
@@ -2599,7 +2599,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E52" t="str">
-        <x:v>校正攻势</x:v>
+        <x:v>购买高级攻击装备</x:v>
       </x:c>
       <x:c r="F52" t="str">
         <x:v>Buqi.Content.EventOption.event_heaven_gate_edge.Name</x:v>
@@ -2610,22 +2610,22 @@
       <x:c r="H52" t="str">
         <x:v>fast</x:v>
       </x:c>
-      <x:c r="I52" t="str"/>
-      <x:c r="J52" t="str"/>
+      <x:c r="I52"/>
+      <x:c r="J52"/>
       <x:c r="K52" t="str">
         <x:v>Coins,4,None</x:v>
       </x:c>
       <x:c r="L52" t="str">
         <x:v>GrantItemTag,1,finisher,0,event-heaven-gate-fast</x:v>
       </x:c>
-      <x:c r="M52" t="str"/>
-      <x:c r="N52" t="str"/>
-      <x:c r="O52" t="str"/>
+      <x:c r="M52"/>
+      <x:c r="N52"/>
+      <x:c r="O52"/>
       <x:c r="P52" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q52" t="str">
-        <x:v>支付 4 灵石，从攻击子池获得一件定型收尾器物。</x:v>
+        <x:v>支付 4 金币，从攻击子池获得一件高级收尾装备。</x:v>
       </x:c>
       <x:c r="R52" t="str">
         <x:v>Buqi.Content.EventOption.event_heaven_gate_edge.Summary</x:v>
@@ -2643,7 +2643,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E53" t="str">
-        <x:v>校正节拍</x:v>
+        <x:v>购买加急改造</x:v>
       </x:c>
       <x:c r="F53" t="str">
         <x:v>Buqi.Content.EventOption.event_heaven_gate_tempo.Name</x:v>
@@ -2654,22 +2654,22 @@
       <x:c r="H53" t="str">
         <x:v>haste</x:v>
       </x:c>
-      <x:c r="I53" t="str"/>
-      <x:c r="J53" t="str"/>
+      <x:c r="I53"/>
+      <x:c r="J53"/>
       <x:c r="K53" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
       <x:c r="L53" t="str">
         <x:v>GrantRefinement,1,A-01,0,event-heaven-gate-tempo</x:v>
       </x:c>
-      <x:c r="M53" t="str"/>
-      <x:c r="N53" t="str"/>
-      <x:c r="O53" t="str"/>
+      <x:c r="M53"/>
+      <x:c r="N53"/>
+      <x:c r="O53"/>
       <x:c r="P53" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q53" t="str">
-        <x:v>支付 2 灵石，获得加急精炼。</x:v>
+        <x:v>支付 2 金币，获得加急改造。</x:v>
       </x:c>
       <x:c r="R53" t="str">
         <x:v>Buqi.Content.EventOption.event_heaven_gate_tempo.Summary</x:v>
@@ -2687,7 +2687,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E54" t="str">
-        <x:v>留下余量</x:v>
+        <x:v>获得攻击装备加速</x:v>
       </x:c>
       <x:c r="F54" t="str">
         <x:v>Buqi.Content.EventOption.event_heaven_gate_spare.Name</x:v>
@@ -2698,22 +2698,22 @@
       <x:c r="H54" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I54" t="str"/>
-      <x:c r="J54" t="str"/>
+      <x:c r="I54"/>
+      <x:c r="J54"/>
       <x:c r="K54" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L54" t="str">
         <x:v>TemporaryHaste,1200,attack,1,event-heaven-gate-haste</x:v>
       </x:c>
-      <x:c r="M54" t="str"/>
-      <x:c r="N54" t="str"/>
-      <x:c r="O54" t="str"/>
+      <x:c r="M54"/>
+      <x:c r="N54"/>
+      <x:c r="O54"/>
       <x:c r="P54" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q54" t="str">
-        <x:v>下一战攻击器物开场加速 1200。</x:v>
+        <x:v>下一战攻击装备开场加速 1200。</x:v>
       </x:c>
       <x:c r="R54" t="str">
         <x:v>Buqi.Content.EventOption.event_heaven_gate_spare.Summary</x:v>
@@ -2731,7 +2731,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E55" t="str">
-        <x:v>封入堡垒</x:v>
+        <x:v>购买高级护盾装备</x:v>
       </x:c>
       <x:c r="F55" t="str">
         <x:v>Buqi.Content.EventOption.event_mountain_eye_seal.Name</x:v>
@@ -2742,22 +2742,22 @@
       <x:c r="H55" t="str">
         <x:v>buffer</x:v>
       </x:c>
-      <x:c r="I55" t="str"/>
-      <x:c r="J55" t="str"/>
+      <x:c r="I55"/>
+      <x:c r="J55"/>
       <x:c r="K55" t="str">
         <x:v>Coins,4,None</x:v>
       </x:c>
       <x:c r="L55" t="str">
         <x:v>GrantItemTag,1,finisher,0,event-mountain-eye-buffer</x:v>
       </x:c>
-      <x:c r="M55" t="str"/>
-      <x:c r="N55" t="str"/>
-      <x:c r="O55" t="str"/>
+      <x:c r="M55"/>
+      <x:c r="N55"/>
+      <x:c r="O55"/>
       <x:c r="P55" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q55" t="str">
-        <x:v>支付 4 灵石，从护体子池获得一件定型收尾器物。</x:v>
+        <x:v>支付 4 金币，从护盾子池获得一件高级收尾装备。</x:v>
       </x:c>
       <x:c r="R55" t="str">
         <x:v>Buqi.Content.EventOption.event_mountain_eye_seal.Summary</x:v>
@@ -2775,7 +2775,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E56" t="str">
-        <x:v>借阵护身</x:v>
+        <x:v>获得开场护盾</x:v>
       </x:c>
       <x:c r="F56" t="str">
         <x:v>Buqi.Content.EventOption.event_mountain_eye_ward.Name</x:v>
@@ -2786,22 +2786,22 @@
       <x:c r="H56" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I56" t="str"/>
-      <x:c r="J56" t="str"/>
+      <x:c r="I56"/>
+      <x:c r="J56"/>
       <x:c r="K56" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
       <x:c r="L56" t="str">
         <x:v>TemporaryBuffer,16,None,1,event-mountain-eye-ward</x:v>
       </x:c>
-      <x:c r="M56" t="str"/>
-      <x:c r="N56" t="str"/>
-      <x:c r="O56" t="str"/>
+      <x:c r="M56"/>
+      <x:c r="N56"/>
+      <x:c r="O56"/>
       <x:c r="P56" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q56" t="str">
-        <x:v>下一战开场获得 16 点护体。</x:v>
+        <x:v>下一战开场获得 16 点护盾。</x:v>
       </x:c>
       <x:c r="R56" t="str">
         <x:v>Buqi.Content.EventOption.event_mountain_eye_ward.Summary</x:v>
@@ -2819,7 +2819,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E57" t="str">
-        <x:v>取一枚阵石</x:v>
+        <x:v>过载换可靠改造</x:v>
       </x:c>
       <x:c r="F57" t="str">
         <x:v>Buqi.Content.EventOption.event_mountain_eye_stone.Name</x:v>
@@ -2830,22 +2830,22 @@
       <x:c r="H57" t="str">
         <x:v>counter</x:v>
       </x:c>
-      <x:c r="I57" t="str"/>
-      <x:c r="J57" t="str"/>
+      <x:c r="I57"/>
+      <x:c r="J57"/>
       <x:c r="K57" t="str">
         <x:v>NoiseDebt,2,None</x:v>
       </x:c>
       <x:c r="L57" t="str">
         <x:v>GrantRefinement,1,A-04,0,event-mountain-eye-stone</x:v>
       </x:c>
-      <x:c r="M57" t="str"/>
-      <x:c r="N57" t="str"/>
-      <x:c r="O57" t="str"/>
+      <x:c r="M57"/>
+      <x:c r="N57"/>
+      <x:c r="O57"/>
       <x:c r="P57" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q57" t="str">
-        <x:v>下一战增加 2 点失衡，获得可靠精炼。</x:v>
+        <x:v>下一战增加 2 点过载，获得可靠改造。</x:v>
       </x:c>
       <x:c r="R57" t="str">
         <x:v>Buqi.Content.EventOption.event_mountain_eye_stone.Summary</x:v>
@@ -2863,7 +2863,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E58" t="str">
-        <x:v>合炼归元汤</x:v>
+        <x:v>购买高级恢复装备</x:v>
       </x:c>
       <x:c r="F58" t="str">
         <x:v>Buqi.Content.EventOption.event_herbs_return_brew.Name</x:v>
@@ -2874,22 +2874,22 @@
       <x:c r="H58" t="str">
         <x:v>heal</x:v>
       </x:c>
-      <x:c r="I58" t="str"/>
-      <x:c r="J58" t="str"/>
+      <x:c r="I58"/>
+      <x:c r="J58"/>
       <x:c r="K58" t="str">
         <x:v>Coins,4,None</x:v>
       </x:c>
       <x:c r="L58" t="str">
         <x:v>GrantItemTag,1,finisher,0,event-herbs-return-heal</x:v>
       </x:c>
-      <x:c r="M58" t="str"/>
-      <x:c r="N58" t="str"/>
-      <x:c r="O58" t="str"/>
+      <x:c r="M58"/>
+      <x:c r="N58"/>
+      <x:c r="O58"/>
       <x:c r="P58" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q58" t="str">
-        <x:v>支付 4 灵石，从恢复子池获得一件定型收尾器物。</x:v>
+        <x:v>支付 4 金币，从恢复子池获得一件高级收尾装备。</x:v>
       </x:c>
       <x:c r="R58" t="str">
         <x:v>Buqi.Content.EventOption.event_herbs_return_brew.Summary</x:v>
@@ -2907,7 +2907,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E59" t="str">
-        <x:v>分饮药汤</x:v>
+        <x:v>获得开场恢复</x:v>
       </x:c>
       <x:c r="F59" t="str">
         <x:v>Buqi.Content.EventOption.event_herbs_return_share.Name</x:v>
@@ -2918,17 +2918,17 @@
       <x:c r="H59" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I59" t="str"/>
-      <x:c r="J59" t="str"/>
+      <x:c r="I59"/>
+      <x:c r="J59"/>
       <x:c r="K59" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
       <x:c r="L59" t="str">
         <x:v>TemporaryHealing,16,None,1,event-herbs-return-rest</x:v>
       </x:c>
-      <x:c r="M59" t="str"/>
-      <x:c r="N59" t="str"/>
-      <x:c r="O59" t="str"/>
+      <x:c r="M59"/>
+      <x:c r="N59"/>
+      <x:c r="O59"/>
       <x:c r="P59" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -2951,7 +2951,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E60" t="str">
-        <x:v>留下药引</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
       <x:c r="F60" t="str">
         <x:v>Buqi.Content.EventOption.event_herbs_return_seed.Name</x:v>
@@ -2962,22 +2962,22 @@
       <x:c r="H60" t="str">
         <x:v>economy</x:v>
       </x:c>
-      <x:c r="I60" t="str"/>
-      <x:c r="J60" t="str"/>
+      <x:c r="I60"/>
+      <x:c r="J60"/>
       <x:c r="K60" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L60" t="str">
         <x:v>Coins,3,None,0,event-herbs-return-coins</x:v>
       </x:c>
-      <x:c r="M60" t="str"/>
-      <x:c r="N60" t="str"/>
-      <x:c r="O60" t="str"/>
+      <x:c r="M60"/>
+      <x:c r="N60"/>
+      <x:c r="O60"/>
       <x:c r="P60" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q60" t="str">
-        <x:v>获得 3 灵石。</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
       <x:c r="R60" t="str">
         <x:v>Buqi.Content.EventOption.event_herbs_return_seed.Summary</x:v>
@@ -2995,7 +2995,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E61" t="str">
-        <x:v>清偿旧约</x:v>
+        <x:v>清除全部欠款</x:v>
       </x:c>
       <x:c r="F61" t="str">
         <x:v>Buqi.Content.EventOption.event_old_pacts_pay.Name</x:v>
@@ -3006,8 +3006,8 @@
       <x:c r="H61" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I61" t="str"/>
-      <x:c r="J61" t="str"/>
+      <x:c r="I61"/>
+      <x:c r="J61"/>
       <x:c r="K61" t="str">
         <x:v>Coins,3,None</x:v>
       </x:c>
@@ -3020,12 +3020,12 @@
       <x:c r="N61" t="str">
         <x:v>ledger_owed|borrowed_flame</x:v>
       </x:c>
-      <x:c r="O61" t="str"/>
+      <x:c r="O61"/>
       <x:c r="P61" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q61" t="str">
-        <x:v>支付 3 灵石，清除账册与火种欠约。</x:v>
+        <x:v>支付 3 金币，清除全部欠款状态。</x:v>
       </x:c>
       <x:c r="R61" t="str">
         <x:v>Buqi.Content.EventOption.event_old_pacts_pay.Summary</x:v>
@@ -3043,7 +3043,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E62" t="str">
-        <x:v>带约入战</x:v>
+        <x:v>过载换超载改造</x:v>
       </x:c>
       <x:c r="F62" t="str">
         <x:v>Buqi.Content.EventOption.event_old_pacts_bear.Name</x:v>
@@ -3054,8 +3054,8 @@
       <x:c r="H62" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I62" t="str"/>
-      <x:c r="J62" t="str"/>
+      <x:c r="I62"/>
+      <x:c r="J62"/>
       <x:c r="K62" t="str">
         <x:v>NoiseDebt,3,None</x:v>
       </x:c>
@@ -3065,13 +3065,13 @@
       <x:c r="M62" t="str">
         <x:v>pacts_settled</x:v>
       </x:c>
-      <x:c r="N62" t="str"/>
-      <x:c r="O62" t="str"/>
+      <x:c r="N62"/>
+      <x:c r="O62"/>
       <x:c r="P62" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q62" t="str">
-        <x:v>下一战增加 3 点失衡，获得超载精炼。</x:v>
+        <x:v>下一战增加 3 点过载，获得超载改造。</x:v>
       </x:c>
       <x:c r="R62" t="str">
         <x:v>Buqi.Content.EventOption.event_old_pacts_bear.Summary</x:v>
@@ -3089,7 +3089,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E63" t="str">
-        <x:v>重订条款</x:v>
+        <x:v>获得购买折扣</x:v>
       </x:c>
       <x:c r="F63" t="str">
         <x:v>Buqi.Content.EventOption.event_old_pacts_rewrite.Name</x:v>
@@ -3100,8 +3100,8 @@
       <x:c r="H63" t="str">
         <x:v>economy</x:v>
       </x:c>
-      <x:c r="I63" t="str"/>
-      <x:c r="J63" t="str"/>
+      <x:c r="I63"/>
+      <x:c r="J63"/>
       <x:c r="K63" t="str">
         <x:v>Coins,1,None</x:v>
       </x:c>
@@ -3111,13 +3111,13 @@
       <x:c r="M63" t="str">
         <x:v>pacts_settled</x:v>
       </x:c>
-      <x:c r="N63" t="str"/>
-      <x:c r="O63" t="str"/>
+      <x:c r="N63"/>
+      <x:c r="O63"/>
       <x:c r="P63" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q63" t="str">
-        <x:v>支付 1 灵石，本日下一次购买少花 2 灵石。</x:v>
+        <x:v>支付 1 金币，本日下一次购买少花 2 金币。</x:v>
       </x:c>
       <x:c r="R63" t="str">
         <x:v>Buqi.Content.EventOption.event_old_pacts_rewrite.Summary</x:v>
@@ -3135,7 +3135,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E64" t="str">
-        <x:v>拆掉起手件</x:v>
+        <x:v>卖出起手装备</x:v>
       </x:c>
       <x:c r="F64" t="str">
         <x:v>Buqi.Content.EventOption.event_scrap_recovery_strip.Name</x:v>
@@ -3146,22 +3146,22 @@
       <x:c r="H64" t="str">
         <x:v>starter</x:v>
       </x:c>
-      <x:c r="I64" t="str"/>
-      <x:c r="J64" t="str"/>
+      <x:c r="I64"/>
+      <x:c r="J64"/>
       <x:c r="K64" t="str">
         <x:v>ItemTag,1,starter</x:v>
       </x:c>
       <x:c r="L64" t="str">
         <x:v>Coins,4,None,0,event-scrap-recovery-starter</x:v>
       </x:c>
-      <x:c r="M64" t="str"/>
-      <x:c r="N64" t="str"/>
-      <x:c r="O64" t="str"/>
+      <x:c r="M64"/>
+      <x:c r="N64"/>
+      <x:c r="O64"/>
       <x:c r="P64" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q64" t="str">
-        <x:v>移除一件起手器物，获得 4 灵石。</x:v>
+        <x:v>移除一件起手装备，获得 4 金币。</x:v>
       </x:c>
       <x:c r="R64" t="str">
         <x:v>Buqi.Content.EventOption.event_scrap_recovery_strip.Summary</x:v>
@@ -3179,7 +3179,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E65" t="str">
-        <x:v>以旧换新</x:v>
+        <x:v>更换转向装备</x:v>
       </x:c>
       <x:c r="F65" t="str">
         <x:v>Buqi.Content.EventOption.event_scrap_recovery_trade.Name</x:v>
@@ -3190,22 +3190,22 @@
       <x:c r="H65" t="str">
         <x:v>pivot</x:v>
       </x:c>
-      <x:c r="I65" t="str"/>
-      <x:c r="J65" t="str"/>
+      <x:c r="I65"/>
+      <x:c r="J65"/>
       <x:c r="K65" t="str">
         <x:v>ItemTag,1,pivot</x:v>
       </x:c>
       <x:c r="L65" t="str">
         <x:v>GrantItemTag,1,counter,0,event-scrap-recovery-counter</x:v>
       </x:c>
-      <x:c r="M65" t="str"/>
-      <x:c r="N65" t="str"/>
-      <x:c r="O65" t="str"/>
+      <x:c r="M65"/>
+      <x:c r="N65"/>
+      <x:c r="O65"/>
       <x:c r="P65" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q65" t="str">
-        <x:v>移除一件转向器物，获得一件改良反制器物。</x:v>
+        <x:v>移除一件转向装备，获得一件强化反制装备。</x:v>
       </x:c>
       <x:c r="R65" t="str">
         <x:v>Buqi.Content.EventOption.event_scrap_recovery_trade.Summary</x:v>
@@ -3223,7 +3223,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E66" t="str">
-        <x:v>替人分拣</x:v>
+        <x:v>获得 3 金币</x:v>
       </x:c>
       <x:c r="F66" t="str">
         <x:v>Buqi.Content.EventOption.event_scrap_recovery_sort.Name</x:v>
@@ -3234,22 +3234,22 @@
       <x:c r="H66" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I66" t="str"/>
-      <x:c r="J66" t="str"/>
+      <x:c r="I66"/>
+      <x:c r="J66"/>
       <x:c r="K66" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L66" t="str">
         <x:v>Coins,3,None,0,event-scrap-recovery-work</x:v>
       </x:c>
-      <x:c r="M66" t="str"/>
-      <x:c r="N66" t="str"/>
-      <x:c r="O66" t="str"/>
+      <x:c r="M66"/>
+      <x:c r="N66"/>
+      <x:c r="O66"/>
       <x:c r="P66" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q66" t="str">
-        <x:v>获得 3 灵石。</x:v>
+        <x:v>获得 3 金币。</x:v>
       </x:c>
       <x:c r="R66" t="str">
         <x:v>Buqi.Content.EventOption.event_scrap_recovery_sort.Summary</x:v>
@@ -3267,7 +3267,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E67" t="str">
-        <x:v>静听一刻</x:v>
+        <x:v>获得护盾与恢复</x:v>
       </x:c>
       <x:c r="F67" t="str">
         <x:v>Buqi.Content.EventOption.event_calming_chime_listen.Name</x:v>
@@ -3278,22 +3278,22 @@
       <x:c r="H67" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I67" t="str"/>
-      <x:c r="J67" t="str"/>
+      <x:c r="I67"/>
+      <x:c r="J67"/>
       <x:c r="K67" t="str">
         <x:v>Coins,1,None</x:v>
       </x:c>
       <x:c r="L67" t="str">
         <x:v>TemporaryBuffer,10,None,1,event-calming-chime-buffer|TemporaryHealing,6,None,1,event-calming-chime-heal</x:v>
       </x:c>
-      <x:c r="M67" t="str"/>
-      <x:c r="N67" t="str"/>
-      <x:c r="O67" t="str"/>
+      <x:c r="M67"/>
+      <x:c r="N67"/>
+      <x:c r="O67"/>
       <x:c r="P67" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q67" t="str">
-        <x:v>支付 1 灵石；下一战开场获得 10 护体并恢复 6 生命。</x:v>
+        <x:v>支付 1 金币；下一战开场获得 10 护盾并恢复 6 生命。</x:v>
       </x:c>
       <x:c r="R67" t="str">
         <x:v>Buqi.Content.EventOption.event_calming_chime_listen.Summary</x:v>
@@ -3311,7 +3311,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E68" t="str">
-        <x:v>调准钟舌</x:v>
+        <x:v>升级反制装备</x:v>
       </x:c>
       <x:c r="F68" t="str">
         <x:v>Buqi.Content.EventOption.event_calming_chime_tune.Name</x:v>
@@ -3322,22 +3322,22 @@
       <x:c r="H68" t="str">
         <x:v>counter</x:v>
       </x:c>
-      <x:c r="I68" t="str"/>
-      <x:c r="J68" t="str"/>
+      <x:c r="I68"/>
+      <x:c r="J68"/>
       <x:c r="K68" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
       <x:c r="L68" t="str">
         <x:v>UpgradeItemTag,1,counter,0,event-calming-chime-upgrade</x:v>
       </x:c>
-      <x:c r="M68" t="str"/>
-      <x:c r="N68" t="str"/>
-      <x:c r="O68" t="str"/>
+      <x:c r="M68"/>
+      <x:c r="N68"/>
+      <x:c r="O68"/>
       <x:c r="P68" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q68" t="str">
-        <x:v>支付 2 灵石，升级一件普通反制器物。</x:v>
+        <x:v>支付 2 金币，升级一件普通反制装备。</x:v>
       </x:c>
       <x:c r="R68" t="str">
         <x:v>Buqi.Content.EventOption.event_calming_chime_tune.Summary</x:v>
@@ -3355,7 +3355,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E69" t="str">
-        <x:v>记下钟律</x:v>
+        <x:v>过载换共享装备</x:v>
       </x:c>
       <x:c r="F69" t="str">
         <x:v>Buqi.Content.EventOption.event_calming_chime_copy.Name</x:v>
@@ -3366,22 +3366,22 @@
       <x:c r="H69" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I69" t="str"/>
-      <x:c r="J69" t="str"/>
+      <x:c r="I69"/>
+      <x:c r="J69"/>
       <x:c r="K69" t="str">
         <x:v>NoiseDebt,2,None</x:v>
       </x:c>
       <x:c r="L69" t="str">
         <x:v>GrantItemTag,1,shared,0,event-calming-chime-shared</x:v>
       </x:c>
-      <x:c r="M69" t="str"/>
-      <x:c r="N69" t="str"/>
-      <x:c r="O69" t="str"/>
+      <x:c r="M69"/>
+      <x:c r="N69"/>
+      <x:c r="O69"/>
       <x:c r="P69" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q69" t="str">
-        <x:v>下一战增加 2 点失衡，获得一件改良共享器物。</x:v>
+        <x:v>下一战增加 2 点过载，获得一件强化共享装备。</x:v>
       </x:c>
       <x:c r="R69" t="str">
         <x:v>Buqi.Content.EventOption.event_calming_chime_copy.Summary</x:v>
@@ -3399,7 +3399,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E70" t="str">
-        <x:v>按攻势结算</x:v>
+        <x:v>攻击构筑结算</x:v>
       </x:c>
       <x:c r="F70" t="str">
         <x:v>Buqi.Content.EventOption.event_day_nine_ledger_attack.Name</x:v>
@@ -3413,23 +3413,23 @@
       <x:c r="I70" t="str">
         <x:v>auction_claim</x:v>
       </x:c>
-      <x:c r="J70" t="str"/>
+      <x:c r="J70"/>
       <x:c r="K70" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L70" t="str">
         <x:v>Coins,5,None,0,event-day-nine-ledger-fast</x:v>
       </x:c>
-      <x:c r="M70" t="str"/>
+      <x:c r="M70"/>
       <x:c r="N70" t="str">
         <x:v>auction_claim</x:v>
       </x:c>
-      <x:c r="O70" t="str"/>
+      <x:c r="O70"/>
       <x:c r="P70" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q70" t="str">
-        <x:v>攻击构筑获得 5 灵石。</x:v>
+        <x:v>攻击构筑获得 5 金币。</x:v>
       </x:c>
       <x:c r="R70" t="str">
         <x:v>Buqi.Content.EventOption.event_day_nine_ledger_attack.Summary</x:v>
@@ -3447,7 +3447,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E71" t="str">
-        <x:v>按守势结算</x:v>
+        <x:v>护盾构筑结算</x:v>
       </x:c>
       <x:c r="F71" t="str">
         <x:v>Buqi.Content.EventOption.event_day_nine_ledger_ward.Name</x:v>
@@ -3461,23 +3461,23 @@
       <x:c r="I71" t="str">
         <x:v>auction_claim</x:v>
       </x:c>
-      <x:c r="J71" t="str"/>
+      <x:c r="J71"/>
       <x:c r="K71" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L71" t="str">
         <x:v>Life,1,None,0,event-day-nine-ledger-buffer</x:v>
       </x:c>
-      <x:c r="M71" t="str"/>
+      <x:c r="M71"/>
       <x:c r="N71" t="str">
         <x:v>auction_claim</x:v>
       </x:c>
-      <x:c r="O71" t="str"/>
+      <x:c r="O71"/>
       <x:c r="P71" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q71" t="str">
-        <x:v>护体构筑恢复 1 命。</x:v>
+        <x:v>护盾构筑恢复 1 命。</x:v>
       </x:c>
       <x:c r="R71" t="str">
         <x:v>Buqi.Content.EventOption.event_day_nine_ledger_ward.Summary</x:v>
@@ -3495,7 +3495,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E72" t="str">
-        <x:v>按续航结算</x:v>
+        <x:v>恢复构筑结算</x:v>
       </x:c>
       <x:c r="F72" t="str">
         <x:v>Buqi.Content.EventOption.event_day_nine_ledger_sustain.Name</x:v>
@@ -3509,23 +3509,23 @@
       <x:c r="I72" t="str">
         <x:v>auction_claim</x:v>
       </x:c>
-      <x:c r="J72" t="str"/>
+      <x:c r="J72"/>
       <x:c r="K72" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L72" t="str">
         <x:v>GrantRefinement,1,A-03,0,event-day-nine-ledger-heal</x:v>
       </x:c>
-      <x:c r="M72" t="str"/>
+      <x:c r="M72"/>
       <x:c r="N72" t="str">
         <x:v>auction_claim</x:v>
       </x:c>
-      <x:c r="O72" t="str"/>
+      <x:c r="O72"/>
       <x:c r="P72" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q72" t="str">
-        <x:v>恢复构筑获得复写精炼。</x:v>
+        <x:v>恢复构筑获得复写改造。</x:v>
       </x:c>
       <x:c r="R72" t="str">
         <x:v>Buqi.Content.EventOption.event_day_nine_ledger_sustain.Summary</x:v>
@@ -3543,7 +3543,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E73" t="str">
-        <x:v>熔去旧起手</x:v>
+        <x:v>移除起手并升级装备</x:v>
       </x:c>
       <x:c r="F73" t="str">
         <x:v>Buqi.Content.EventOption.event_return_furnace_finish.Name</x:v>
@@ -3554,22 +3554,22 @@
       <x:c r="H73" t="str">
         <x:v>starter</x:v>
       </x:c>
-      <x:c r="I73" t="str"/>
-      <x:c r="J73" t="str"/>
+      <x:c r="I73"/>
+      <x:c r="J73"/>
       <x:c r="K73" t="str">
         <x:v>ItemTag,1,starter</x:v>
       </x:c>
       <x:c r="L73" t="str">
         <x:v>UpgradeItemTag,1,finisher,0,event-return-furnace-finish</x:v>
       </x:c>
-      <x:c r="M73" t="str"/>
-      <x:c r="N73" t="str"/>
-      <x:c r="O73" t="str"/>
+      <x:c r="M73"/>
+      <x:c r="N73"/>
+      <x:c r="O73"/>
       <x:c r="P73" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q73" t="str">
-        <x:v>移除一件起手器物，将一件收尾器物提升一级。</x:v>
+        <x:v>移除一件起手装备，将一件收尾装备提升一级。</x:v>
       </x:c>
       <x:c r="R73" t="str">
         <x:v>Buqi.Content.EventOption.event_return_furnace_finish.Summary</x:v>
@@ -3587,7 +3587,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E74" t="str">
-        <x:v>重排三路</x:v>
+        <x:v>购买高级转向装备</x:v>
       </x:c>
       <x:c r="F74" t="str">
         <x:v>Buqi.Content.EventOption.event_return_furnace_balance.Name</x:v>
@@ -3598,22 +3598,22 @@
       <x:c r="H74" t="str">
         <x:v>bridge</x:v>
       </x:c>
-      <x:c r="I74" t="str"/>
-      <x:c r="J74" t="str"/>
+      <x:c r="I74"/>
+      <x:c r="J74"/>
       <x:c r="K74" t="str">
         <x:v>Coins,2,None</x:v>
       </x:c>
       <x:c r="L74" t="str">
         <x:v>GrantItemTag,1,pivot,0,event-return-furnace-pivot</x:v>
       </x:c>
-      <x:c r="M74" t="str"/>
-      <x:c r="N74" t="str"/>
-      <x:c r="O74" t="str"/>
+      <x:c r="M74"/>
+      <x:c r="N74"/>
+      <x:c r="O74"/>
       <x:c r="P74" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q74" t="str">
-        <x:v>支付 2 灵石，获得一件定型转向器物。</x:v>
+        <x:v>支付 2 金币，获得一件高级转向装备。</x:v>
       </x:c>
       <x:c r="R74" t="str">
         <x:v>Buqi.Content.EventOption.event_return_furnace_balance.Summary</x:v>
@@ -3631,7 +3631,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E75" t="str">
-        <x:v>封存余火</x:v>
+        <x:v>恢复生命并清除状态</x:v>
       </x:c>
       <x:c r="F75" t="str">
         <x:v>Buqi.Content.EventOption.event_return_furnace_close.Name</x:v>
@@ -3642,24 +3642,24 @@
       <x:c r="H75" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="I75" t="str"/>
-      <x:c r="J75" t="str"/>
+      <x:c r="I75"/>
+      <x:c r="J75"/>
       <x:c r="K75" t="str">
         <x:v>None,0,None</x:v>
       </x:c>
       <x:c r="L75" t="str">
         <x:v>Life,1,None,0,event-return-furnace-life</x:v>
       </x:c>
-      <x:c r="M75" t="str"/>
+      <x:c r="M75"/>
       <x:c r="N75" t="str">
         <x:v>ledger_owed|borrowed_flame|umbrella_borrowed|auction_claim</x:v>
       </x:c>
-      <x:c r="O75" t="str"/>
+      <x:c r="O75"/>
       <x:c r="P75" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="Q75" t="str">
-        <x:v>恢复 1 命并清除全部跨日约记。</x:v>
+        <x:v>恢复 1 命并清除全部跨日状态。</x:v>
       </x:c>
       <x:c r="R75" t="str">
         <x:v>Buqi.Content.EventOption.event_return_furnace_close.Summary</x:v>
